--- a/TestData/UploadFiles/LoginRequest.xlsx
+++ b/TestData/UploadFiles/LoginRequest.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView windowWidth="23040" windowHeight="9000" firstSheet="0" activeTab="2"/>
+    <x:workbookView windowWidth="28800" windowHeight="12180" firstSheet="0" activeTab="1"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Roles" sheetId="1" r:id="rId1"/>
@@ -98,13 +98,13 @@
     <x:t>eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5...</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:03.2318906Z</x:t>
+    <x:t>2026-09-28T14:06:13.6523250Z</x:t>
   </x:si>
   <x:si>
     <x:t>2026-07-03T19:49:23.6888430Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:25:52.2925007Z</x:t>
+    <x:t>2026-09-28T08:28:56.0385018Z</x:t>
   </x:si>
   <x:si>
     <x:t>ParentRole</x:t>
@@ -125,7 +125,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-08T10:26:04.8705957Z</x:t>
+    <x:t>2026-09-28T14:13:01.2982484Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -807,8 +807,8 @@
     <x:cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </x:cellStyles>
   <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{D912C4B3-9C32-4402-94F0-D5C7ECBC8C95}"/>
-    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{963F0849-76DD-41AF-9355-CB1212D29E49}"/>
+    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{8D9C8483-5A64-4691-A339-07560C8A25A5}"/>
+    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{FD70FDF4-DA72-4C38-819E-2EF78B968594}"/>
   </x:tableStyles>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1106,14 +1106,14 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:F5"/>
-  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="14.4"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16.444444" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10.555556" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.447619" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.552381" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="39" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="54.222222" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="54.219048" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="40.666667" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16.111111" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.114286" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6">
@@ -1231,9 +1231,11 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:D5"/>
-  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="14.4"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.222222" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.714286" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -1321,12 +1323,12 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:D4"/>
-  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="14.4"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.444444" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14.888889" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.111111" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.571429" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.714286" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.885714" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.114286" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">

--- a/TestData/UploadFiles/LoginRequest.xlsx
+++ b/TestData/UploadFiles/LoginRequest.xlsx
@@ -98,13 +98,13 @@
     <x:t>eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5...</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T14:06:13.6523250Z</x:t>
+    <x:t>2026-09-28T20:53:15.3668258Z</x:t>
   </x:si>
   <x:si>
     <x:t>2026-07-03T19:49:23.6888430Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T08:28:56.0385018Z</x:t>
+    <x:t>2026-09-28T19:10:09.8993942Z</x:t>
   </x:si>
   <x:si>
     <x:t>ParentRole</x:t>
@@ -125,7 +125,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T14:13:01.2982484Z</x:t>
+    <x:t>2026-09-28T20:53:36.6418699Z</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/LoginRequest.xlsx
+++ b/TestData/UploadFiles/LoginRequest.xlsx
@@ -98,13 +98,13 @@
     <x:t>eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5...</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T20:53:15.3668258Z</x:t>
+    <x:t>2026-09-29T05:45:17.9386926Z</x:t>
   </x:si>
   <x:si>
     <x:t>2026-07-03T19:49:23.6888430Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T19:10:09.8993942Z</x:t>
+    <x:t>2026-09-29T05:44:27.3617829Z</x:t>
   </x:si>
   <x:si>
     <x:t>ParentRole</x:t>
@@ -125,7 +125,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-28T20:53:36.6418699Z</x:t>
+    <x:t>2026-09-29T12:25:24.7724424Z</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/LoginRequest.xlsx
+++ b/TestData/UploadFiles/LoginRequest.xlsx
@@ -98,7 +98,7 @@
     <x:t>eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5...</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T05:45:17.9386926Z</x:t>
+    <x:t>2026-10-05T11:28:20.1082106Z</x:t>
   </x:si>
   <x:si>
     <x:t>2026-07-03T19:49:23.6888430Z</x:t>
@@ -125,7 +125,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-29T12:25:24.7724424Z</x:t>
+    <x:t>2026-10-05T13:14:43.1421137Z</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/LoginRequest.xlsx
+++ b/TestData/UploadFiles/LoginRequest.xlsx
@@ -83,6 +83,15 @@
     <x:t>AdminRole</x:t>
   </x:si>
   <x:si>
+    <x:t>BannerRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Banner1@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoviPass@123</x:t>
+  </x:si>
+  <x:si>
     <x:t>HttpStatus</x:t>
   </x:si>
   <x:si>
@@ -107,6 +116,9 @@
     <x:t>2026-09-29T05:44:27.3617829Z</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-10-07T12:46:16.7198531Z</x:t>
+  </x:si>
+  <x:si>
     <x:t>ParentRole</x:t>
   </x:si>
   <x:si>
@@ -125,7 +137,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-05T13:14:43.1421137Z</x:t>
+    <x:t>2026-10-07T13:24:54.5855122Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1216,6 +1228,26 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" spans="1:6">
+      <x:c r="A6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1243,13 +1275,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1257,13 +1289,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
@@ -1271,13 +1303,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -1285,13 +1317,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
@@ -1299,13 +1331,27 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1333,21 +1379,21 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>13</x:v>
@@ -1356,12 +1402,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>11</x:v>
@@ -1370,12 +1416,12 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>6</x:v>
@@ -1384,7 +1430,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/LoginRequest.xlsx
+++ b/TestData/UploadFiles/LoginRequest.xlsx
@@ -137,7 +137,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T13:24:54.5855122Z</x:t>
+    <x:t>2026-10-08T11:23:03.7539341Z</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/LoginRequest.xlsx
+++ b/TestData/UploadFiles/LoginRequest.xlsx
@@ -116,7 +116,7 @@
     <x:t>2026-09-29T05:44:27.3617829Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-07T12:46:16.7198531Z</x:t>
+    <x:t>2026-10-09T13:07:59.8390589Z</x:t>
   </x:si>
   <x:si>
     <x:t>ParentRole</x:t>
@@ -137,7 +137,7 @@
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-08T11:23:03.7539341Z</x:t>
+    <x:t>2026-10-09T13:52:55.2630490Z</x:t>
   </x:si>
 </x:sst>
 </file>
